--- a/business_forms/016_firmographics_survey--business_forms.xlsx
+++ b/business_forms/016_firmographics_survey--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>company_size</t>
+          <t>is_large_organization</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>company_size</t>
+          <t>Is your company large?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>number_of_employees</t>
+          <t>Number of Employees</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>company_industry</t>
+          <t>Company Industry</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>company_location</t>
+          <t>Company Location</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>company_type</t>
+          <t>company_founder</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>company_type</t>
+          <t>Company Founder</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,40 +653,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>company_founder</t>
+          <t>number_of_offices</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>company_founder</t>
+          <t>Number of Offices</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>number_of_offices</t>
+          <t>established_date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>number_of_offices</t>
+          <t>Established Date</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>established_date</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>established_date</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>Contact Person</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>contact_phone</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>Contact Phone</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,18 +796,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>company_industry_other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>company_industry_other</t>
+          <t>company_location_other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Company Location Other</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>company_industry_other_other</t>
+          <t>number_of_offices_other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other (other)</t>
+          <t>Number Of Offices Other</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>company_location_other</t>
+          <t>established_date_other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Established Date Other</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>number_of_offices_other</t>
+          <t>contact_phone_other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Contact Phone Other</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>established_date_other</t>
+          <t>company_founder_other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Company Founder Other</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>contact_phone_other</t>
+          <t>website_other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Website Other</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,131 +957,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>contact_email_other</t>
+          <t>established_year</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Established Year</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>company_founder_other</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>contact_person_other</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>established_year</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>established_year</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>company_size_other</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>website_other</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1101,9 +986,9 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,7 +1011,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>company_size_choices</t>
+          <t>is_large_organization_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1028,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>company_size_choices</t>
+          <t>is_large_organization_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1165,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
@@ -1182,46 +1067,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>company_type_choices</t>
+          <t>company_location_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>company_type_choices</t>
+          <t>company_location_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
